--- a/outputs/49237.xlsx
+++ b/outputs/49237.xlsx
@@ -271,103 +271,103 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -389,7 +389,6 @@
         <color rgb="FF000000"/>
         <sz val="11"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -648,7 +647,7 @@
     <row r="1" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="2" t="n">
         <f aca="true">TODAY()</f>
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>

--- a/outputs/49237.xlsx
+++ b/outputs/49237.xlsx
@@ -776,8 +776,8 @@
         <v>Veteran</v>
       </c>
       <c r="F7" s="1" t="str">
-        <f aca="false">IF(F10="","",LEFT(F10)&amp;".")</f>
-        <v>G.</v>
+        <f aca="false">IF(LEN(F10)&gt;0,F10&amp;".","")</f>
+        <v>George.</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
